--- a/Final Model/Forecasts/model_warnings.xlsx
+++ b/Final Model/Forecasts/model_warnings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="warnings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'warnings'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'warnings'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -650,8 +650,1000 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>newest generic ballot poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-04 (25 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>newest approval poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-06 (23 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>polls dropped for missing nominees</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>112 of 486 VoteHub rows (old hypothetical match-ups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>coverage: Kansas</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5 polls (effective 1.9), Kalshi 48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>coverage: Nebraska</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.5), Kalshi 32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>coverage: South Carolina</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.1), Kalshi 28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>newest generic ballot poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-04 (26 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>newest approval poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-06 (24 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>polls dropped for missing nominees</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>112 of 486 VoteHub rows (old hypothetical match-ups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>coverage: Kansas</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5 polls (effective 1.9), Kalshi 48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>coverage: Nebraska</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.5), Kalshi 32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>coverage: South Carolina</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.1), Kalshi 28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>newest generic ballot poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-04 (26 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>newest approval poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-06 (24 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>polls dropped for missing nominees</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>112 of 486 VoteHub rows (old hypothetical match-ups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>coverage: Kansas</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>5 polls (effective 1.9), Kalshi 48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>coverage: Nebraska</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.5), Kalshi 32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>coverage: South Carolina</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.1), Kalshi 28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>newest generic ballot poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-04 (26 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>newest approval poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-06 (24 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>polls dropped for missing nominees</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>112 of 486 VoteHub rows (old hypothetical match-ups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>coverage: Kansas</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5 polls (effective 1.9), Kalshi 48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>coverage: Nebraska</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.5), Kalshi 32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>coverage: South Carolina</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.1), Kalshi 28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>newest generic ballot poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-04 (26 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>newest approval poll (VoteHub)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-06 (24 days old) - Kalshi averages fill the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>polls dropped for missing nominees</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>112 of 486 VoteHub rows (old hypothetical match-ups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>national: generic ballot (D-R)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10 VoteHub polls (= 1.1 fresh polls) + Kalshi counted as 0 -&gt; +8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>coverage: Kansas</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5 polls (effective 1.9), Kalshi 52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>coverage: Nebraska</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.5), Kalshi 32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>coverage: South Carolina</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4 polls (effective 2.1), Kalshi 28%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>